--- a/simtab/demo/demo_simtab.xlsx
+++ b/simtab/demo/demo_simtab.xlsx
@@ -60,7 +60,7 @@
     <t>+0.01</t>
   </si>
   <si>
-    <t>-0.00</t>
+    <t>0.00</t>
   </si>
   <si>
     <t>+0.04</t>
